--- a/backend/data/financials_by_company/1616.HK.xlsx
+++ b/backend/data/financials_by_company/1616.HK.xlsx
@@ -692,212 +692,222 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-118549250</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>-28064000</v>
+        <v>-173400000</v>
       </c>
       <c r="E2" t="n">
-        <v>7585000</v>
+        <v>-325840000</v>
       </c>
       <c r="F2" t="n">
-        <v>7585000</v>
+        <v>-474197000</v>
       </c>
       <c r="G2" t="n">
-        <v>-38598000</v>
+        <v>-533848000</v>
       </c>
       <c r="H2" t="n">
-        <v>2311000</v>
+        <v>8349000</v>
       </c>
       <c r="I2" t="n">
-        <v>39132000</v>
+        <v>109913000</v>
       </c>
       <c r="J2" t="n">
-        <v>-20479000</v>
+        <v>-499240000</v>
       </c>
       <c r="K2" t="n">
-        <v>-22790000</v>
+        <v>-507589000</v>
       </c>
       <c r="L2" t="n">
-        <v>-15578000</v>
+        <v>-5919000</v>
       </c>
       <c r="M2" t="n">
-        <v>15808000</v>
+        <v>15121000</v>
       </c>
       <c r="N2" t="n">
-        <v>241000</v>
+        <v>9932000</v>
       </c>
       <c r="O2" t="n">
-        <v>-46183000</v>
+        <v>-29843250</v>
       </c>
       <c r="P2" t="n">
-        <v>-38598000</v>
+        <v>-533848000</v>
       </c>
       <c r="Q2" t="n">
-        <v>51647000</v>
+        <v>141385000</v>
       </c>
       <c r="R2" t="n">
-        <v>-22193000</v>
+        <v>-506756000</v>
       </c>
       <c r="S2" t="n">
-        <v>2151577000</v>
+        <v>1798733000</v>
       </c>
       <c r="T2" t="n">
-        <v>2151577000</v>
+        <v>1798733000</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0179</v>
+        <v>-0.2968</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0179</v>
+        <v>-0.2968</v>
       </c>
       <c r="W2" t="n">
-        <v>-38598000</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
+        <v>-533848000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
       <c r="Y2" t="n">
-        <v>-38598000</v>
+        <v>-533848000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-38598000</v>
+        <v>-533848000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>270000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-38598000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>-534118000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-38598000</v>
+        <v>-534118000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>11408000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-38598000</v>
+        <v>-522710000</v>
       </c>
       <c r="AH2" t="n">
-        <v>7364000</v>
+        <v>2264000</v>
       </c>
       <c r="AI2" t="n">
-        <v>7585000</v>
+        <v>-480996000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-4615000</v>
+        <v>-2590000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2970000</v>
+        <v>314380000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>22091000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-1242000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>-15578000</v>
+        <v>-5919000</v>
       </c>
       <c r="AO2" t="n">
-        <v>11000</v>
+        <v>730000</v>
       </c>
       <c r="AP2" t="n">
-        <v>15808000</v>
+        <v>15121000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>241000</v>
+        <v>9932000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-34971000</v>
+        <v>-45276000</v>
       </c>
       <c r="AS2" t="n">
-        <v>12515000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
+        <v>31472000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>202015000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
       <c r="AV2" t="n">
-        <v>12515000</v>
+        <v>31472000</v>
       </c>
       <c r="AW2" t="n">
-        <v>3536000</v>
+        <v>8175000</v>
       </c>
       <c r="AX2" t="n">
-        <v>8979000</v>
+        <v>23297000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-22456000</v>
+        <v>-13804000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>39132000</v>
+        <v>109913000</v>
       </c>
       <c r="BA2" t="n">
-        <v>16676000</v>
+        <v>96109000</v>
       </c>
       <c r="BB2" t="n">
-        <v>16676000</v>
+        <v>96109000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-1079310.675298</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.006752</v>
       </c>
       <c r="D3" t="n">
-        <v>-70187000</v>
+        <v>-48261000</v>
       </c>
       <c r="E3" t="n">
-        <v>67808000</v>
+        <v>-159848000</v>
       </c>
       <c r="F3" t="n">
-        <v>67808000</v>
+        <v>-159848000</v>
       </c>
       <c r="G3" t="n">
-        <v>-15645000</v>
+        <v>-223794000</v>
       </c>
       <c r="H3" t="n">
-        <v>2645000</v>
+        <v>10047000</v>
       </c>
       <c r="I3" t="n">
-        <v>77116000</v>
+        <v>72482000</v>
       </c>
       <c r="J3" t="n">
-        <v>-2379000</v>
+        <v>-208109000</v>
       </c>
       <c r="K3" t="n">
-        <v>-5024000</v>
+        <v>-218156000</v>
       </c>
       <c r="L3" t="n">
-        <v>-8318000</v>
+        <v>-6528000</v>
       </c>
       <c r="M3" t="n">
-        <v>10686000</v>
+        <v>11402000</v>
       </c>
       <c r="N3" t="n">
-        <v>2386000</v>
+        <v>4879000</v>
       </c>
       <c r="O3" t="n">
-        <v>-83453000</v>
+        <v>-65025310.675298</v>
       </c>
       <c r="P3" t="n">
-        <v>-15645000</v>
+        <v>-223794000</v>
       </c>
       <c r="Q3" t="n">
-        <v>99407000</v>
+        <v>122411000</v>
       </c>
       <c r="R3" t="n">
-        <v>-6774000</v>
+        <v>-219563000</v>
       </c>
       <c r="S3" t="n">
         <v>2151577000</v>
@@ -906,154 +916,156 @@
         <v>2151577000</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0073</v>
+        <v>-0.104</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0073</v>
+        <v>-0.104</v>
       </c>
       <c r="W3" t="n">
-        <v>-15645000</v>
+        <v>-223794000</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-15645000</v>
+        <v>-223794000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-15645000</v>
+        <v>-223794000</v>
       </c>
       <c r="AB3" t="n">
-        <v>65000</v>
+        <v>4214000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-15710000</v>
+        <v>-228008000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-15710000</v>
+        <v>-228008000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>-1550000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-15710000</v>
+        <v>-229558000</v>
       </c>
       <c r="AH3" t="n">
-        <v>2293000</v>
+        <v>10469000</v>
       </c>
       <c r="AI3" t="n">
-        <v>68101000</v>
+        <v>-162049000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-74503000</v>
+        <v>-7832000</v>
       </c>
       <c r="AK3" t="n">
-        <v>5902000</v>
+        <v>169881000</v>
       </c>
       <c r="AL3" t="n">
-        <v>500000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
       <c r="AN3" t="n">
-        <v>-8318000</v>
+        <v>-6528000</v>
       </c>
       <c r="AO3" t="n">
-        <v>18000</v>
+        <v>5000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10686000</v>
+        <v>11402000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2386000</v>
+        <v>4879000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-75659000</v>
+        <v>-84319000</v>
       </c>
       <c r="AS3" t="n">
-        <v>22291000</v>
+        <v>49929000</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6611000</v>
       </c>
       <c r="AV3" t="n">
-        <v>22291000</v>
+        <v>43318000</v>
       </c>
       <c r="AW3" t="n">
-        <v>4496000</v>
+        <v>10295000</v>
       </c>
       <c r="AX3" t="n">
-        <v>17795000</v>
+        <v>33023000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-53368000</v>
+        <v>-34390000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>77116000</v>
+        <v>72482000</v>
       </c>
       <c r="BA3" t="n">
-        <v>23748000</v>
+        <v>38092000</v>
       </c>
       <c r="BB3" t="n">
-        <v>23748000</v>
+        <v>38092000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-1079310.675298</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006752</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-48261000</v>
+        <v>-70187000</v>
       </c>
       <c r="E4" t="n">
-        <v>-159848000</v>
+        <v>67808000</v>
       </c>
       <c r="F4" t="n">
-        <v>-159848000</v>
+        <v>67808000</v>
       </c>
       <c r="G4" t="n">
-        <v>-223794000</v>
+        <v>-15645000</v>
       </c>
       <c r="H4" t="n">
-        <v>10047000</v>
+        <v>2645000</v>
       </c>
       <c r="I4" t="n">
-        <v>72482000</v>
+        <v>77116000</v>
       </c>
       <c r="J4" t="n">
-        <v>-208109000</v>
+        <v>-2379000</v>
       </c>
       <c r="K4" t="n">
-        <v>-218156000</v>
+        <v>-5024000</v>
       </c>
       <c r="L4" t="n">
-        <v>-6528000</v>
+        <v>-8318000</v>
       </c>
       <c r="M4" t="n">
-        <v>11402000</v>
+        <v>10686000</v>
       </c>
       <c r="N4" t="n">
-        <v>4879000</v>
+        <v>2386000</v>
       </c>
       <c r="O4" t="n">
-        <v>-65025310.675298</v>
+        <v>-83453000</v>
       </c>
       <c r="P4" t="n">
-        <v>-223794000</v>
+        <v>-15645000</v>
       </c>
       <c r="Q4" t="n">
-        <v>122411000</v>
+        <v>99407000</v>
       </c>
       <c r="R4" t="n">
-        <v>-219563000</v>
+        <v>-6774000</v>
       </c>
       <c r="S4" t="n">
         <v>2151577000</v>
@@ -1062,264 +1074,252 @@
         <v>2151577000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.104</v>
+        <v>-0.0073</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.104</v>
+        <v>-0.0073</v>
       </c>
       <c r="W4" t="n">
-        <v>-223794000</v>
+        <v>-15645000</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>-223794000</v>
+        <v>-15645000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-223794000</v>
+        <v>-15645000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4214000</v>
+        <v>65000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-228008000</v>
+        <v>-15710000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-228008000</v>
+        <v>-15710000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1550000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-229558000</v>
+        <v>-15710000</v>
       </c>
       <c r="AH4" t="n">
-        <v>10469000</v>
+        <v>2293000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-162049000</v>
+        <v>68101000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-7832000</v>
+        <v>-74503000</v>
       </c>
       <c r="AK4" t="n">
-        <v>169881000</v>
+        <v>5902000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
+        <v>500000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>-6528000</v>
+        <v>-8318000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="AP4" t="n">
-        <v>11402000</v>
+        <v>10686000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4879000</v>
+        <v>2386000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-84319000</v>
+        <v>-75659000</v>
       </c>
       <c r="AS4" t="n">
-        <v>49929000</v>
+        <v>22291000</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>6611000</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>43318000</v>
+        <v>22291000</v>
       </c>
       <c r="AW4" t="n">
-        <v>10295000</v>
+        <v>4496000</v>
       </c>
       <c r="AX4" t="n">
-        <v>33023000</v>
+        <v>17795000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-34390000</v>
+        <v>-53368000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>72482000</v>
+        <v>77116000</v>
       </c>
       <c r="BA4" t="n">
-        <v>38092000</v>
+        <v>23748000</v>
       </c>
       <c r="BB4" t="n">
-        <v>38092000</v>
+        <v>23748000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-118549250</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-173400000</v>
+        <v>-28064000</v>
       </c>
       <c r="E5" t="n">
-        <v>-325840000</v>
+        <v>7585000</v>
       </c>
       <c r="F5" t="n">
-        <v>-474197000</v>
+        <v>7585000</v>
       </c>
       <c r="G5" t="n">
-        <v>-533848000</v>
+        <v>-38598000</v>
       </c>
       <c r="H5" t="n">
-        <v>8349000</v>
+        <v>2311000</v>
       </c>
       <c r="I5" t="n">
-        <v>109913000</v>
+        <v>39132000</v>
       </c>
       <c r="J5" t="n">
-        <v>-499240000</v>
+        <v>-20479000</v>
       </c>
       <c r="K5" t="n">
-        <v>-507589000</v>
+        <v>-22790000</v>
       </c>
       <c r="L5" t="n">
-        <v>-5919000</v>
+        <v>-15578000</v>
       </c>
       <c r="M5" t="n">
-        <v>15121000</v>
+        <v>15808000</v>
       </c>
       <c r="N5" t="n">
-        <v>9932000</v>
+        <v>241000</v>
       </c>
       <c r="O5" t="n">
-        <v>-29843250</v>
+        <v>-46183000</v>
       </c>
       <c r="P5" t="n">
-        <v>-533848000</v>
+        <v>-38598000</v>
       </c>
       <c r="Q5" t="n">
-        <v>141385000</v>
+        <v>51647000</v>
       </c>
       <c r="R5" t="n">
-        <v>-506756000</v>
+        <v>-22193000</v>
       </c>
       <c r="S5" t="n">
-        <v>1798733000</v>
+        <v>2151577000</v>
       </c>
       <c r="T5" t="n">
-        <v>1798733000</v>
+        <v>2151577000</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2968</v>
+        <v>-0.0179</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2968</v>
+        <v>-0.0179</v>
       </c>
       <c r="W5" t="n">
-        <v>-533848000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
+        <v>-38598000</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>-533848000</v>
+        <v>-38598000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-533848000</v>
+        <v>-38598000</v>
       </c>
       <c r="AB5" t="n">
-        <v>270000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-534118000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>-38598000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-534118000</v>
+        <v>-38598000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11408000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-522710000</v>
+        <v>-38598000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2264000</v>
+        <v>7364000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-480996000</v>
+        <v>7585000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-2590000</v>
+        <v>-4615000</v>
       </c>
       <c r="AK5" t="n">
-        <v>314380000</v>
+        <v>-2970000</v>
       </c>
       <c r="AL5" t="n">
-        <v>22091000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1242000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>-5919000</v>
+        <v>-15578000</v>
       </c>
       <c r="AO5" t="n">
-        <v>730000</v>
+        <v>11000</v>
       </c>
       <c r="AP5" t="n">
-        <v>15121000</v>
+        <v>15808000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9932000</v>
+        <v>241000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-45276000</v>
+        <v>-34971000</v>
       </c>
       <c r="AS5" t="n">
-        <v>31472000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>202015000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
+        <v>12515000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>31472000</v>
+        <v>12515000</v>
       </c>
       <c r="AW5" t="n">
-        <v>8175000</v>
+        <v>3536000</v>
       </c>
       <c r="AX5" t="n">
-        <v>23297000</v>
+        <v>8979000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-13804000</v>
+        <v>-22456000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>109913000</v>
+        <v>39132000</v>
       </c>
       <c r="BA5" t="n">
-        <v>96109000</v>
+        <v>16676000</v>
       </c>
       <c r="BB5" t="n">
-        <v>96109000</v>
+        <v>16676000</v>
       </c>
     </row>
   </sheetData>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>2151577026</v>
@@ -1659,42 +1659,44 @@
         <v>2151577026</v>
       </c>
       <c r="D2" t="n">
-        <v>76186000</v>
+        <v>86063000</v>
       </c>
       <c r="E2" t="n">
-        <v>89533000</v>
+        <v>147715000</v>
       </c>
       <c r="F2" t="n">
-        <v>155525000</v>
+        <v>403640000</v>
       </c>
       <c r="G2" t="n">
-        <v>254058000</v>
+        <v>558372000</v>
       </c>
       <c r="H2" t="n">
-        <v>148654000</v>
+        <v>262469000</v>
       </c>
       <c r="I2" t="n">
-        <v>155525000</v>
+        <v>403640000</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>26154000</v>
       </c>
       <c r="K2" t="n">
-        <v>164525000</v>
+        <v>436811000</v>
       </c>
       <c r="L2" t="n">
-        <v>164525000</v>
+        <v>436811000</v>
       </c>
       <c r="M2" t="n">
-        <v>164525000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>439271000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2460000</v>
+      </c>
       <c r="O2" t="n">
-        <v>164525000</v>
+        <v>436811000</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>-918661000</v>
+        <v>-728864000</v>
       </c>
       <c r="R2" t="n">
         <v>857469000</v>
@@ -1706,124 +1708,136 @@
         <v>137801000</v>
       </c>
       <c r="U2" t="n">
-        <v>116282000</v>
+        <v>345819000</v>
       </c>
       <c r="V2" t="n">
-        <v>539000</v>
+        <v>26204000</v>
       </c>
       <c r="W2" t="n">
-        <v>539000</v>
+        <v>5268000</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>20936000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>20936000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
-        <v>115743000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>319615000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>12927000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>89533000</v>
+        <v>126779000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>5218000</v>
       </c>
       <c r="AE2" t="n">
-        <v>89533000</v>
+        <v>121561000</v>
       </c>
       <c r="AF2" t="n">
-        <v>23209000</v>
+        <v>170867000</v>
       </c>
       <c r="AG2" t="n">
-        <v>3690000</v>
+        <v>15902000</v>
       </c>
       <c r="AH2" t="n">
-        <v>14130000</v>
+        <v>63180000</v>
       </c>
       <c r="AI2" t="n">
-        <v>5389000</v>
+        <v>91785000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>280807000</v>
+        <v>785090000</v>
       </c>
       <c r="AK2" t="n">
-        <v>16410000</v>
+        <v>203006000</v>
       </c>
       <c r="AL2" t="n">
-        <v>7324000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>130942000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1870000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1870000</v>
       </c>
       <c r="AP2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>20000</v>
-      </c>
+        <v>1870000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1870000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>9000000</v>
+        <v>33171000</v>
       </c>
       <c r="AT2" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>33171000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
       <c r="AV2" t="n">
-        <v>66000</v>
+        <v>5405000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-86000</v>
+        <v>-41324000</v>
       </c>
       <c r="AX2" t="n">
-        <v>152000</v>
+        <v>46729000</v>
       </c>
       <c r="AY2" t="n">
-        <v>152000</v>
+        <v>3211000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>43518000</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>264397000</v>
+        <v>582084000</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>888000</v>
       </c>
       <c r="BD2" t="n">
-        <v>228128000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>104251000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>15197000</v>
+      </c>
       <c r="BF2" t="n">
-        <v>6279000</v>
+        <v>348119000</v>
       </c>
       <c r="BG2" t="n">
-        <v>16643000</v>
+        <v>78131000</v>
       </c>
       <c r="BH2" t="n">
-        <v>13347000</v>
+        <v>35498000</v>
       </c>
       <c r="BI2" t="n">
-        <v>13347000</v>
+        <v>35498000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13347000</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
+        <v>35498000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>2151577026</v>
@@ -1831,43 +1845,47 @@
       <c r="C3" t="n">
         <v>2151577026</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>101421000</v>
+      </c>
       <c r="E3" t="n">
-        <v>87082000</v>
+        <v>123922000</v>
       </c>
       <c r="F3" t="n">
-        <v>192123000</v>
+        <v>205768000</v>
       </c>
       <c r="G3" t="n">
-        <v>289755000</v>
+        <v>331079000</v>
       </c>
       <c r="H3" t="n">
-        <v>142727000</v>
+        <v>93629000</v>
       </c>
       <c r="I3" t="n">
-        <v>192123000</v>
+        <v>205768000</v>
       </c>
       <c r="J3" t="n">
-        <v>450000</v>
+        <v>11611000</v>
       </c>
       <c r="K3" t="n">
-        <v>203123000</v>
+        <v>218768000</v>
       </c>
       <c r="L3" t="n">
-        <v>203123000</v>
+        <v>218768000</v>
       </c>
       <c r="M3" t="n">
-        <v>203123000</v>
+        <v>218523000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-245000</v>
       </c>
       <c r="O3" t="n">
-        <v>203123000</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>218768000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5751000</v>
+      </c>
       <c r="Q3" t="n">
-        <v>-880377000</v>
+        <v>-952658000</v>
       </c>
       <c r="R3" t="n">
         <v>857469000</v>
@@ -1879,130 +1897,132 @@
         <v>137801000</v>
       </c>
       <c r="U3" t="n">
-        <v>122030000</v>
+        <v>317807000</v>
       </c>
       <c r="V3" t="n">
-        <v>814000</v>
+        <v>14657000</v>
       </c>
       <c r="W3" t="n">
-        <v>539000</v>
+        <v>3718000</v>
       </c>
       <c r="X3" t="n">
-        <v>275000</v>
+        <v>10939000</v>
       </c>
       <c r="Y3" t="n">
-        <v>275000</v>
+        <v>10939000</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>121216000</v>
+        <v>303150000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1600000</v>
+        <v>12796000</v>
       </c>
       <c r="AC3" t="n">
-        <v>86807000</v>
+        <v>112983000</v>
       </c>
       <c r="AD3" t="n">
-        <v>175000</v>
+        <v>672000</v>
       </c>
       <c r="AE3" t="n">
-        <v>86632000</v>
+        <v>112311000</v>
       </c>
       <c r="AF3" t="n">
-        <v>29808000</v>
+        <v>168505000</v>
       </c>
       <c r="AG3" t="n">
-        <v>6863000</v>
+        <v>17123000</v>
       </c>
       <c r="AH3" t="n">
-        <v>15438000</v>
+        <v>63234000</v>
       </c>
       <c r="AI3" t="n">
-        <v>7507000</v>
+        <v>88148000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>325153000</v>
+        <v>536330000</v>
       </c>
       <c r="AK3" t="n">
-        <v>61210000</v>
+        <v>139551000</v>
       </c>
       <c r="AL3" t="n">
-        <v>48104000</v>
+        <v>92402000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>1577000</v>
+        <v>1870000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1577000</v>
+        <v>1870000</v>
       </c>
       <c r="AP3" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>11000000</v>
+        <v>13000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>11000000</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>13000000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
       <c r="AV3" t="n">
-        <v>509000</v>
+        <v>250000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-168000</v>
+        <v>-18801000</v>
       </c>
       <c r="AX3" t="n">
-        <v>677000</v>
+        <v>19051000</v>
       </c>
       <c r="AY3" t="n">
-        <v>132000</v>
+        <v>2921000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>545000</v>
+        <v>16130000</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>263943000</v>
+        <v>396779000</v>
       </c>
       <c r="BC3" t="n">
-        <v>10000</v>
+        <v>550000</v>
       </c>
       <c r="BD3" t="n">
-        <v>9415000</v>
+        <v>59994000</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>15448000</v>
       </c>
       <c r="BF3" t="n">
-        <v>9329000</v>
+        <v>230319000</v>
       </c>
       <c r="BG3" t="n">
-        <v>8441000</v>
+        <v>79578000</v>
       </c>
       <c r="BH3" t="n">
-        <v>236748000</v>
+        <v>10890000</v>
       </c>
       <c r="BI3" t="n">
-        <v>236748000</v>
+        <v>10890000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>236748000</v>
+        <v>10871000</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>2151577026</v>
@@ -2010,47 +2030,43 @@
       <c r="C4" t="n">
         <v>2151577026</v>
       </c>
-      <c r="D4" t="n">
-        <v>101421000</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>123922000</v>
+        <v>87082000</v>
       </c>
       <c r="F4" t="n">
-        <v>205768000</v>
+        <v>192123000</v>
       </c>
       <c r="G4" t="n">
-        <v>331079000</v>
+        <v>289755000</v>
       </c>
       <c r="H4" t="n">
-        <v>93629000</v>
+        <v>142727000</v>
       </c>
       <c r="I4" t="n">
-        <v>205768000</v>
+        <v>192123000</v>
       </c>
       <c r="J4" t="n">
-        <v>11611000</v>
+        <v>450000</v>
       </c>
       <c r="K4" t="n">
-        <v>218768000</v>
+        <v>203123000</v>
       </c>
       <c r="L4" t="n">
-        <v>218768000</v>
+        <v>203123000</v>
       </c>
       <c r="M4" t="n">
-        <v>218523000</v>
+        <v>203123000</v>
       </c>
       <c r="N4" t="n">
-        <v>-245000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>218768000</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5751000</v>
-      </c>
+        <v>203123000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>-952658000</v>
+        <v>-880377000</v>
       </c>
       <c r="R4" t="n">
         <v>857469000</v>
@@ -2062,132 +2078,130 @@
         <v>137801000</v>
       </c>
       <c r="U4" t="n">
-        <v>317807000</v>
+        <v>122030000</v>
       </c>
       <c r="V4" t="n">
-        <v>14657000</v>
+        <v>814000</v>
       </c>
       <c r="W4" t="n">
-        <v>3718000</v>
+        <v>539000</v>
       </c>
       <c r="X4" t="n">
-        <v>10939000</v>
+        <v>275000</v>
       </c>
       <c r="Y4" t="n">
-        <v>10939000</v>
+        <v>275000</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>303150000</v>
+        <v>121216000</v>
       </c>
       <c r="AB4" t="n">
-        <v>12796000</v>
+        <v>1600000</v>
       </c>
       <c r="AC4" t="n">
-        <v>112983000</v>
+        <v>86807000</v>
       </c>
       <c r="AD4" t="n">
-        <v>672000</v>
+        <v>175000</v>
       </c>
       <c r="AE4" t="n">
-        <v>112311000</v>
+        <v>86632000</v>
       </c>
       <c r="AF4" t="n">
-        <v>168505000</v>
+        <v>29808000</v>
       </c>
       <c r="AG4" t="n">
-        <v>17123000</v>
+        <v>6863000</v>
       </c>
       <c r="AH4" t="n">
-        <v>63234000</v>
+        <v>15438000</v>
       </c>
       <c r="AI4" t="n">
-        <v>88148000</v>
+        <v>7507000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>536330000</v>
+        <v>325153000</v>
       </c>
       <c r="AK4" t="n">
-        <v>139551000</v>
+        <v>61210000</v>
       </c>
       <c r="AL4" t="n">
-        <v>92402000</v>
+        <v>48104000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>1870000</v>
+        <v>1577000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1870000</v>
+        <v>1577000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AS4" t="n">
-        <v>13000000</v>
+        <v>11000000</v>
       </c>
       <c r="AT4" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
+        <v>11000000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>250000</v>
+        <v>509000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-18801000</v>
+        <v>-168000</v>
       </c>
       <c r="AX4" t="n">
-        <v>19051000</v>
+        <v>677000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2921000</v>
+        <v>132000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16130000</v>
+        <v>545000</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>396779000</v>
+        <v>263943000</v>
       </c>
       <c r="BC4" t="n">
-        <v>550000</v>
+        <v>10000</v>
       </c>
       <c r="BD4" t="n">
-        <v>59994000</v>
+        <v>9415000</v>
       </c>
       <c r="BE4" t="n">
-        <v>15448000</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>230319000</v>
+        <v>9329000</v>
       </c>
       <c r="BG4" t="n">
-        <v>79578000</v>
+        <v>8441000</v>
       </c>
       <c r="BH4" t="n">
-        <v>10890000</v>
+        <v>236748000</v>
       </c>
       <c r="BI4" t="n">
-        <v>10890000</v>
+        <v>236748000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>10871000</v>
+        <v>236748000</v>
       </c>
       <c r="BK4" t="n">
-        <v>19000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>2151577026</v>
@@ -2196,44 +2210,42 @@
         <v>2151577026</v>
       </c>
       <c r="D5" t="n">
-        <v>86063000</v>
+        <v>76186000</v>
       </c>
       <c r="E5" t="n">
-        <v>147715000</v>
+        <v>89533000</v>
       </c>
       <c r="F5" t="n">
-        <v>403640000</v>
+        <v>155525000</v>
       </c>
       <c r="G5" t="n">
-        <v>558372000</v>
+        <v>254058000</v>
       </c>
       <c r="H5" t="n">
-        <v>262469000</v>
+        <v>148654000</v>
       </c>
       <c r="I5" t="n">
-        <v>403640000</v>
+        <v>155525000</v>
       </c>
       <c r="J5" t="n">
-        <v>26154000</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>436811000</v>
+        <v>164525000</v>
       </c>
       <c r="L5" t="n">
-        <v>436811000</v>
+        <v>164525000</v>
       </c>
       <c r="M5" t="n">
-        <v>439271000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2460000</v>
-      </c>
+        <v>164525000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>436811000</v>
+        <v>164525000</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>-728864000</v>
+        <v>-918661000</v>
       </c>
       <c r="R5" t="n">
         <v>857469000</v>
@@ -2245,132 +2257,120 @@
         <v>137801000</v>
       </c>
       <c r="U5" t="n">
-        <v>345819000</v>
+        <v>116282000</v>
       </c>
       <c r="V5" t="n">
-        <v>26204000</v>
+        <v>539000</v>
       </c>
       <c r="W5" t="n">
-        <v>5268000</v>
+        <v>539000</v>
       </c>
       <c r="X5" t="n">
-        <v>20936000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>20936000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>319615000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12927000</v>
-      </c>
+        <v>115743000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>126779000</v>
+        <v>89533000</v>
       </c>
       <c r="AD5" t="n">
-        <v>5218000</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>121561000</v>
+        <v>89533000</v>
       </c>
       <c r="AF5" t="n">
-        <v>170867000</v>
+        <v>23209000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15902000</v>
+        <v>3690000</v>
       </c>
       <c r="AH5" t="n">
-        <v>63180000</v>
+        <v>14130000</v>
       </c>
       <c r="AI5" t="n">
-        <v>91785000</v>
+        <v>5389000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>785090000</v>
+        <v>280807000</v>
       </c>
       <c r="AK5" t="n">
-        <v>203006000</v>
+        <v>16410000</v>
       </c>
       <c r="AL5" t="n">
-        <v>130942000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+        <v>7324000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>1870000</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1870000</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1870000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1870000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>20000</v>
+      </c>
       <c r="AS5" t="n">
-        <v>33171000</v>
+        <v>9000000</v>
       </c>
       <c r="AT5" t="n">
-        <v>33171000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
+        <v>9000000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>5405000</v>
+        <v>66000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-41324000</v>
+        <v>-86000</v>
       </c>
       <c r="AX5" t="n">
-        <v>46729000</v>
+        <v>152000</v>
       </c>
       <c r="AY5" t="n">
-        <v>3211000</v>
+        <v>152000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>43518000</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>582084000</v>
+        <v>264397000</v>
       </c>
       <c r="BC5" t="n">
-        <v>888000</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>104251000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>15197000</v>
-      </c>
+        <v>228128000</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>348119000</v>
+        <v>6279000</v>
       </c>
       <c r="BG5" t="n">
-        <v>78131000</v>
+        <v>16643000</v>
       </c>
       <c r="BH5" t="n">
-        <v>35498000</v>
+        <v>13347000</v>
       </c>
       <c r="BI5" t="n">
-        <v>35498000</v>
+        <v>13347000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>35498000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
+        <v>13347000</v>
+      </c>
+      <c r="BK5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2620,530 +2620,530 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1153000</v>
+        <v>29868000</v>
       </c>
       <c r="C2" t="n">
-        <v>-5704000</v>
+        <v>-77000000</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>43000000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12946000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-20000</v>
+        <v>-691000</v>
       </c>
       <c r="G2" t="n">
-        <v>13347000</v>
+        <v>35498000</v>
       </c>
       <c r="H2" t="n">
-        <v>236748000</v>
+        <v>12351000</v>
       </c>
       <c r="I2" t="n">
-        <v>1290000</v>
+        <v>-3396000</v>
       </c>
       <c r="J2" t="n">
-        <v>-224691000</v>
+        <v>26543000</v>
       </c>
       <c r="K2" t="n">
-        <v>-14128000</v>
+        <v>-40352000</v>
       </c>
       <c r="L2" t="n">
-        <v>-131000</v>
+        <v>-8960000</v>
       </c>
       <c r="M2" t="n">
-        <v>-24000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-888000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>12946000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12946000</v>
+      </c>
       <c r="P2" t="n">
-        <v>-5704000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>-34000000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-35500000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>43000000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-5704000</v>
+        <v>-41500000</v>
       </c>
       <c r="U2" t="n">
-        <v>-5704000</v>
+        <v>-41500000</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>43000000</v>
       </c>
       <c r="W2" t="n">
-        <v>-211736000</v>
+        <v>36336000</v>
       </c>
       <c r="X2" t="n">
-        <v>241000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+        <v>3293000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
       <c r="Z2" t="n">
-        <v>1842000</v>
+        <v>126459000</v>
       </c>
       <c r="AA2" t="n">
-        <v>1842000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
+        <v>126459000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-20000</v>
+        <v>-691000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-20000</v>
+        <v>-691000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1173000</v>
+        <v>30559000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1010000</v>
+        <v>-64000</v>
       </c>
       <c r="AG2" t="n">
-        <v>30951000</v>
+        <v>65989000</v>
       </c>
       <c r="AH2" t="n">
-        <v>39200000</v>
+        <v>-40372000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-1042000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>18995000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-37294000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>-7207000</v>
+        <v>87366000</v>
       </c>
       <c r="AL2" t="n">
-        <v>15663000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>3947000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
       <c r="AN2" t="n">
-        <v>2311000</v>
+        <v>8349000</v>
       </c>
       <c r="AO2" t="n">
-        <v>2000000</v>
+        <v>2575000</v>
       </c>
       <c r="AP2" t="n">
-        <v>311000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>5774000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-9389000</v>
+      </c>
       <c r="AR2" t="n">
-        <v>-463000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>-391000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
       <c r="AT2" t="n">
-        <v>-4711000</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-38598000</v>
+        <v>-522710000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>48699000</v>
+        <v>-97722000</v>
       </c>
       <c r="C3" t="n">
-        <v>-29600000</v>
+        <v>-32200000</v>
       </c>
       <c r="D3" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>17000000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-579000</v>
+        <v>-6383000</v>
       </c>
       <c r="G3" t="n">
-        <v>236748000</v>
+        <v>10890000</v>
       </c>
       <c r="H3" t="n">
-        <v>10890000</v>
+        <v>35498000</v>
       </c>
       <c r="I3" t="n">
-        <v>3834000</v>
+        <v>173000</v>
       </c>
       <c r="J3" t="n">
-        <v>222024000</v>
+        <v>-24781000</v>
       </c>
       <c r="K3" t="n">
-        <v>-39989000</v>
+        <v>-24482000</v>
       </c>
       <c r="L3" t="n">
-        <v>-8350000</v>
+        <v>-795000</v>
       </c>
       <c r="M3" t="n">
-        <v>-29000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>-625000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>-20800000</v>
+        <v>-15200000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-20800000</v>
+        <v>-15200000</v>
       </c>
       <c r="R3" t="n">
-        <v>-29600000</v>
+        <v>-32200000</v>
       </c>
       <c r="S3" t="n">
-        <v>8800000</v>
+        <v>17000000</v>
       </c>
       <c r="T3" t="n">
-        <v>-20800000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-29600000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8800000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>212735000</v>
+        <v>91040000</v>
       </c>
       <c r="X3" t="n">
-        <v>2386000</v>
+        <v>4879000</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>38066000</v>
+        <v>92573000</v>
       </c>
       <c r="AA3" t="n">
-        <v>42505000</v>
+        <v>92573000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4439000</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-579000</v>
+        <v>-6383000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-579000</v>
+        <v>-6383000</v>
       </c>
       <c r="AE3" t="n">
-        <v>49278000</v>
+        <v>-91339000</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>125067000</v>
+        <v>-47244000</v>
       </c>
       <c r="AH3" t="n">
-        <v>44455000</v>
+        <v>-100381000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-27837000</v>
+        <v>40074000</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>108449000</v>
+        <v>13063000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3058000</v>
+        <v>-697000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>5751000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2645000</v>
+        <v>10047000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2000000</v>
+        <v>8710000</v>
       </c>
       <c r="AP3" t="n">
-        <v>645000</v>
+        <v>1337000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>293000</v>
+        <v>-2201000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3216000</v>
+        <v>3294000</v>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>-63145000</v>
+        <v>-612000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-15710000</v>
+        <v>-229558000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-97722000</v>
+        <v>48699000</v>
       </c>
       <c r="C4" t="n">
-        <v>-32200000</v>
+        <v>-29600000</v>
       </c>
       <c r="D4" t="n">
-        <v>17000000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>8800000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-6383000</v>
+        <v>-579000</v>
       </c>
       <c r="G4" t="n">
+        <v>236748000</v>
+      </c>
+      <c r="H4" t="n">
         <v>10890000</v>
       </c>
-      <c r="H4" t="n">
-        <v>35498000</v>
-      </c>
       <c r="I4" t="n">
-        <v>173000</v>
+        <v>3834000</v>
       </c>
       <c r="J4" t="n">
-        <v>-24781000</v>
+        <v>222024000</v>
       </c>
       <c r="K4" t="n">
-        <v>-24482000</v>
+        <v>-39989000</v>
       </c>
       <c r="L4" t="n">
-        <v>-795000</v>
+        <v>-8350000</v>
       </c>
       <c r="M4" t="n">
-        <v>-625000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
+        <v>-29000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-15200000</v>
+        <v>-20800000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-15200000</v>
+        <v>-20800000</v>
       </c>
       <c r="R4" t="n">
-        <v>-32200000</v>
+        <v>-29600000</v>
       </c>
       <c r="S4" t="n">
-        <v>17000000</v>
+        <v>8800000</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-20800000</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>-29600000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8800000</v>
+      </c>
       <c r="W4" t="n">
-        <v>91040000</v>
+        <v>212735000</v>
       </c>
       <c r="X4" t="n">
-        <v>4879000</v>
+        <v>2386000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>92573000</v>
+        <v>38066000</v>
       </c>
       <c r="AA4" t="n">
-        <v>92573000</v>
+        <v>42505000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>-4439000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-6383000</v>
+        <v>-579000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-6383000</v>
+        <v>-579000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-91339000</v>
+        <v>49278000</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>-47244000</v>
+        <v>125067000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-100381000</v>
+        <v>44455000</v>
       </c>
       <c r="AI4" t="n">
-        <v>40074000</v>
+        <v>-27837000</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>13063000</v>
+        <v>108449000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-697000</v>
+        <v>-3058000</v>
       </c>
       <c r="AM4" t="n">
-        <v>5751000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>10047000</v>
+        <v>2645000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8710000</v>
+        <v>2000000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1337000</v>
+        <v>645000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-2201000</v>
+        <v>293000</v>
       </c>
       <c r="AR4" t="n">
-        <v>3294000</v>
+        <v>-3216000</v>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-612000</v>
+        <v>-63145000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-229558000</v>
+        <v>-15710000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>29868000</v>
+        <v>1153000</v>
       </c>
       <c r="C5" t="n">
-        <v>-77000000</v>
+        <v>-5704000</v>
       </c>
       <c r="D5" t="n">
-        <v>43000000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>12946000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-691000</v>
+        <v>-20000</v>
       </c>
       <c r="G5" t="n">
-        <v>35498000</v>
+        <v>13347000</v>
       </c>
       <c r="H5" t="n">
-        <v>12351000</v>
+        <v>236748000</v>
       </c>
       <c r="I5" t="n">
-        <v>-3396000</v>
+        <v>1290000</v>
       </c>
       <c r="J5" t="n">
-        <v>26543000</v>
+        <v>-224691000</v>
       </c>
       <c r="K5" t="n">
-        <v>-40352000</v>
+        <v>-14128000</v>
       </c>
       <c r="L5" t="n">
-        <v>-8960000</v>
+        <v>-131000</v>
       </c>
       <c r="M5" t="n">
-        <v>-888000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>12946000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>12946000</v>
-      </c>
+        <v>-24000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-34000000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-35500000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>43000000</v>
-      </c>
+        <v>-5704000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-41500000</v>
+        <v>-5704000</v>
       </c>
       <c r="U5" t="n">
-        <v>-41500000</v>
+        <v>-5704000</v>
       </c>
       <c r="V5" t="n">
-        <v>43000000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>36336000</v>
+        <v>-211736000</v>
       </c>
       <c r="X5" t="n">
-        <v>3293000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
+        <v>241000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>126459000</v>
+        <v>1842000</v>
       </c>
       <c r="AA5" t="n">
-        <v>126459000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>1842000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
       <c r="AC5" t="n">
-        <v>-691000</v>
+        <v>-20000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-691000</v>
+        <v>-20000</v>
       </c>
       <c r="AE5" t="n">
-        <v>30559000</v>
+        <v>1173000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-64000</v>
+        <v>-1010000</v>
       </c>
       <c r="AG5" t="n">
-        <v>65989000</v>
+        <v>30951000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-40372000</v>
+        <v>39200000</v>
       </c>
       <c r="AI5" t="n">
-        <v>18995000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-37294000</v>
-      </c>
+        <v>-1042000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>87366000</v>
+        <v>-7207000</v>
       </c>
       <c r="AL5" t="n">
-        <v>3947000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+        <v>15663000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>8349000</v>
+        <v>2311000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2575000</v>
+        <v>2000000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5774000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-9389000</v>
-      </c>
+        <v>311000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>-391000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
+        <v>-463000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-4711000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-522710000</v>
+        <v>-38598000</v>
       </c>
     </row>
   </sheetData>
@@ -3703,162 +3703,162 @@
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EK1" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Qinyan  Yang', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 335948, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiyou  Liu', 'age': 45, 'title': 'Chief Financial Officer', 'yearBorn': 1980, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Qinyan  Yang', 'title': 'Executive Director', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Qiaoyun  Sun', 'age': 55, 'title': 'Financial Controller', 'yearBorn': 1970, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yin Wah  Chan FCCA, FCIS, FCS, HKICS', 'age': 50, 'title': 'Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Qinyan  Yang', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2024, 'totalPay': 335680, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiyou  Liu', 'age': 45, 'title': 'Chief Financial Officer', 'yearBorn': 1980, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Qinyan  Yang', 'title': 'Executive Director', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Qiaoyun  Sun', 'age': 55, 'title': 'Financial Controller', 'yearBorn': 1970, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yin Wah  Chan FCCA, FCIS, FCS, HKICS', 'age': 50, 'title': 'Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.747</v>
+        <v>-0.76</v>
       </c>
       <c r="AE2" t="n">
         <v>129596000</v>
@@ -4078,10 +4078,10 @@
         <v>2151577026</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.08801877499999999</v>
+        <v>0.08797207</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.68167275</v>
+        <v>0.6820347</v>
       </c>
       <c r="BJ2" t="n">
         <v>1735603200</v>
@@ -4105,10 +4105,10 @@
         <v>-9.077</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1</v>
+        <v>0.8181819</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BS2" t="n">
         <v>0.01205</v>
@@ -4252,119 +4252,119 @@
       <c r="DD2" t="b">
         <v>0</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>Starrise Media Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DF2" t="n">
+      <c r="DO2" t="n">
         <v>1755158883</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>A METAVERSE</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>A Metaverse Company</t>
+        </is>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1342056600000</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.009999998</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>0.047 - 0.06</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>0.034999996</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1.3999999</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>0.025 - 0.06</t>
+        </is>
+      </c>
+      <c r="EB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>81.818184</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1743427270</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1743427270</v>
+      </c>
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="EI2" t="n">
         <v>19.999996</v>
       </c>
-      <c r="DH2" t="n">
+      <c r="EJ2" t="n">
         <v>0.06</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>A Metaverse Company</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>A METAVERSE</t>
-        </is>
-      </c>
-      <c r="DL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1342056600000</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.009999998</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>0.047 - 0.06</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.034999996</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1.3999999</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>0.025 - 0.06</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>100</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1743427270</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1743427270</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Starrise Media Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
       </c>
       <c r="EK2" t="inlineStr"/>
     </row>
